--- a/docs/テスト設計・テストケース・自動テスト対応表・バグ報告.xlsx
+++ b/docs/テスト設計・テストケース・自動テスト対応表・バグ報告.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yoris\OneDrive\デスクトップ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fd2d96f25975b16b/デスクトップ/djangotask/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E48A7AD-1984-47B0-B5B2-609E58F227DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{8E48A7AD-1984-47B0-B5B2-609E58F227DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A656A1FC-4A3D-4ABE-8A7C-120606441B80}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{4C697509-1199-4654-A3C4-8F37DC743BAF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4C697509-1199-4654-A3C4-8F37DC743BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="テストケース・実行結果" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="492">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -4088,12 +4088,53 @@
     <t>test_task_list_requires_authentication/未認証ではタスク一覧へアクセスできない</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>OK率</t>
+    <rPh sb="2" eb="3">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG率</t>
+    <rPh sb="2" eb="3">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>総テスト数</t>
+    <rPh sb="0" eb="1">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自動化率</t>
+    <rPh sb="0" eb="4">
+      <t>ジドウカリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一部対応</t>
+    <rPh sb="0" eb="2">
+      <t>イチブ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4188,6 +4229,14 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -4212,12 +4261,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4290,8 +4342,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="パーセント" xfId="1" builtinId="5"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
@@ -4647,7 +4703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3013DB45-BDAF-4201-A34B-11EDA55BC73D}">
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:N62"/>
   <sheetFormatPr defaultRowHeight="19.8"/>
   <cols>
     <col min="1" max="1" width="4.19921875" customWidth="1"/>
@@ -4660,9 +4716,10 @@
     <col min="8" max="8" width="13.09765625" style="2" customWidth="1"/>
     <col min="9" max="9" width="20.59765625" customWidth="1"/>
     <col min="10" max="10" width="20.69921875" style="5" customWidth="1"/>
+    <col min="12" max="12" width="10.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1">
+    <row r="1" spans="1:14" s="1" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4696,8 +4753,17 @@
       <c r="K1" s="12" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="73.8" customHeight="1">
+      <c r="L1" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="N1" s="12" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="73.8" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -4729,8 +4795,20 @@
       <c r="K2" s="2" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="73.8" customHeight="1">
+      <c r="L2">
+        <f>COUNTA(A2:A60)</f>
+        <v>57</v>
+      </c>
+      <c r="M2" s="24">
+        <f>COUNTIF(K2:K100,"OK")/(COUNTIF(K2:K100,"OK")+COUNTIF(K2:K100,"NG"))</f>
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <f>COUNTIF(K2:K100,"NG")/(COUNTIF(K2:K100,"NG")+COUNTIF(K2:K100,"OK"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="73.8" customHeight="1">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -4763,7 +4841,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="73.8" customHeight="1">
+    <row r="4" spans="1:14" ht="73.8" customHeight="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -4796,7 +4874,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="73.8" customHeight="1">
+    <row r="5" spans="1:14" ht="73.8" customHeight="1">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -4829,7 +4907,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="91.2" customHeight="1">
+    <row r="6" spans="1:14" ht="91.2" customHeight="1">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -4862,7 +4940,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="73.8" customHeight="1">
+    <row r="7" spans="1:14" ht="73.8" customHeight="1">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -4895,7 +4973,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="73.8" customHeight="1">
+    <row r="8" spans="1:14" ht="73.8" customHeight="1">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -4928,7 +5006,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="73.8" customHeight="1">
+    <row r="9" spans="1:14" ht="73.8" customHeight="1">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -4961,7 +5039,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="73.8" customHeight="1">
+    <row r="10" spans="1:14" ht="73.8" customHeight="1">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -4994,7 +5072,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="73.8" customHeight="1">
+    <row r="11" spans="1:14" ht="73.8" customHeight="1">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -5027,7 +5105,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="73.8" customHeight="1">
+    <row r="12" spans="1:14" ht="73.8" customHeight="1">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -5060,7 +5138,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="73.8" customHeight="1">
+    <row r="13" spans="1:14" ht="73.8" customHeight="1">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -5093,7 +5171,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="73.8" customHeight="1">
+    <row r="14" spans="1:14" ht="73.8" customHeight="1">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -5126,7 +5204,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="73.8" customHeight="1">
+    <row r="15" spans="1:14" ht="73.8" customHeight="1">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -5159,7 +5237,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="73.8" customHeight="1">
+    <row r="16" spans="1:14" ht="73.8" customHeight="1">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -6612,7 +6690,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA33B504-C23E-4D73-A479-97B297259FB6}">
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="4.296875" customWidth="1"/>
@@ -6624,7 +6702,7 @@
     <col min="7" max="7" width="19.69921875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="14" customFormat="1">
+    <row r="1" spans="1:10" s="14" customFormat="1">
       <c r="A1" s="14" t="s">
         <v>340</v>
       </c>
@@ -6646,8 +6724,17 @@
       <c r="G1" s="20" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="50.4" customHeight="1">
+      <c r="H1" s="14" t="s">
+        <v>490</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="50.4" customHeight="1">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6666,8 +6753,20 @@
       <c r="F2" s="2" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="35.4" customHeight="1">
+      <c r="H2" s="24">
+        <f>COUNTIF(D2:D100,"〇")/COUNTA(D2:D100)</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I2">
+        <f>COUNTIF(D2:D100,"△")</f>
+        <v>7</v>
+      </c>
+      <c r="J2">
+        <f>COUNTIF(D2:D100,"－")</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="35.4" customHeight="1">
       <c r="A3">
         <v>2</v>
       </c>
@@ -6687,7 +6786,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="35.4" customHeight="1">
+    <row r="4" spans="1:10" ht="35.4" customHeight="1">
       <c r="A4">
         <v>3</v>
       </c>
@@ -6707,7 +6806,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="35.4" customHeight="1">
+    <row r="5" spans="1:10" ht="35.4" customHeight="1">
       <c r="A5">
         <v>4</v>
       </c>
@@ -6727,7 +6826,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="35.4" customHeight="1">
+    <row r="6" spans="1:10" ht="35.4" customHeight="1">
       <c r="A6">
         <v>5</v>
       </c>
@@ -6747,7 +6846,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="35.4" customHeight="1">
+    <row r="7" spans="1:10" ht="35.4" customHeight="1">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6767,7 +6866,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="35.4" customHeight="1">
+    <row r="8" spans="1:10" ht="35.4" customHeight="1">
       <c r="A8">
         <v>7</v>
       </c>
@@ -6787,7 +6886,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="35.4" customHeight="1">
+    <row r="9" spans="1:10" ht="35.4" customHeight="1">
       <c r="A9">
         <v>8</v>
       </c>
@@ -6807,7 +6906,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="35.4" customHeight="1">
+    <row r="10" spans="1:10" ht="35.4" customHeight="1">
       <c r="A10">
         <v>9</v>
       </c>
@@ -6827,7 +6926,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="35.4" customHeight="1">
+    <row r="11" spans="1:10" ht="35.4" customHeight="1">
       <c r="A11">
         <v>10</v>
       </c>
@@ -6847,7 +6946,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="35.4" customHeight="1">
+    <row r="12" spans="1:10" ht="35.4" customHeight="1">
       <c r="A12">
         <v>11</v>
       </c>
@@ -6867,7 +6966,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="35.4" customHeight="1">
+    <row r="13" spans="1:10" ht="35.4" customHeight="1">
       <c r="A13">
         <v>12</v>
       </c>
@@ -6887,7 +6986,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="35.4" customHeight="1">
+    <row r="14" spans="1:10" ht="35.4" customHeight="1">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6907,7 +7006,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="35.4" customHeight="1">
+    <row r="15" spans="1:10" ht="35.4" customHeight="1">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6927,7 +7026,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="35.4" customHeight="1">
+    <row r="16" spans="1:10" ht="35.4" customHeight="1">
       <c r="A16">
         <v>15</v>
       </c>
